--- a/data/3.8.2/0. base-year_2015/system/Y.xlsx
+++ b/data/3.8.2/0. base-year_2015/system/Y.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4BB4C12BCE64FC72EA6BC7221A78775E663234DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\3.8.2\0. base-year_2015\system\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A81834-2663-42E9-94B6-A98E4296AC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -826,7 +832,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1186,9 +1192,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K404"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="5" max="5" width="29.15234375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1210,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1220,7 +1229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1243,7 +1252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1260,7 +1269,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1295,7 +1304,7 @@
         <v>6.4566767702190022</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1322,7 +1331,7 @@
         <v>14718.08180721065</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1349,7 +1358,7 @@
         <v>20417.112299019151</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1376,7 +1385,7 @@
         <v>6796.8505159999986</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1403,7 +1412,7 @@
         <v>1955.228000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1430,7 +1439,7 @@
         <v>13.179087999999989</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1457,7 +1466,7 @@
         <v>3.7881479999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1484,7 +1493,7 @@
         <v>611.75365599999986</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1513,7 +1522,7 @@
         <v>1330.936482330527</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1540,7 +1549,7 @@
         <v>82.643926809008292</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1567,7 +1576,7 @@
         <v>312.08075814018667</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1594,7 +1603,7 @@
         <v>306.44176024233809</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1621,7 +1630,7 @@
         <v>193.44322019063341</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1648,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1675,7 +1684,7 @@
         <v>3.95317935661084</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1702,7 +1711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1729,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1758,7 +1767,7 @@
         <v>3621.1819650000011</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1787,7 +1796,7 @@
         <v>92.024933000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
@@ -1818,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1845,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1872,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1899,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1926,7 +1935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1953,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1980,7 +1989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2007,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2034,7 +2043,7 @@
         <v>40.253296196142053</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2061,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2088,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2115,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2144,7 +2153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2171,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2198,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2225,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2252,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2279,7 +2288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2306,7 +2315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2333,7 +2342,7 @@
         <v>28.669000000000018</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2362,7 +2371,7 @@
         <v>1598.853465999998</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2389,7 +2398,7 @@
         <v>9098.3076190000047</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2416,7 +2425,7 @@
         <v>1930.3016120000009</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2" t="s">
@@ -2447,7 +2456,7 @@
         <v>1026.089497727821</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2474,7 +2483,7 @@
         <v>867.69036708812064</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2501,7 +2510,7 @@
         <v>1369.601276286726</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2528,7 +2537,7 @@
         <v>1332.5322730648011</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2555,7 +2564,7 @@
         <v>916.76191730870482</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2582,7 +2591,7 @@
         <v>7167.815984951676</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2609,7 +2618,7 @@
         <v>61.220073034121221</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2636,7 +2645,7 @@
         <v>1109.6417842333101</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2663,7 +2672,7 @@
         <v>16786.129942528711</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2690,7 +2699,7 @@
         <v>16372.583764088709</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2717,7 +2726,7 @@
         <v>1020.644371969256</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2744,7 +2753,7 @@
         <v>298.64657478554409</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2773,7 +2782,7 @@
         <v>5200.7769891073303</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2800,7 +2809,7 @@
         <v>8080.5672469815463</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2827,7 +2836,7 @@
         <v>2916.308003536963</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2856,7 +2865,7 @@
         <v>1365.30845383107</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2885,7 +2894,7 @@
         <v>842.40401003292095</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2914,7 +2923,7 @@
         <v>238.43990927425159</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2943,7 +2952,7 @@
         <v>376.04758380762911</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2972,7 +2981,7 @@
         <v>6317.6222374304498</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3001,7 +3010,7 @@
         <v>2375.194705784847</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
@@ -3032,7 +3041,7 @@
         <v>18.043574629867749</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3059,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3086,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3115,7 +3124,7 @@
         <v>4315.0003856872399</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3142,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3169,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3196,7 +3205,7 @@
         <v>1143.1112288703821</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3223,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3250,7 +3259,7 @@
         <v>2784.7205868002252</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3279,7 +3288,7 @@
         <v>6228.712787295286</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3306,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3335,7 +3344,7 @@
         <v>1351.7476010737021</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3364,7 +3373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3391,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3418,7 +3427,7 @@
         <v>2991.3644331387732</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3445,7 +3454,7 @@
         <v>41.655999999999977</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3472,7 +3481,7 @@
         <v>152.48700000000011</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3499,7 +3508,7 @@
         <v>241.62389593811849</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3526,7 +3535,7 @@
         <v>40.127000000000073</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3553,7 +3562,7 @@
         <v>23.531729505956839</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3580,7 +3589,7 @@
         <v>629.17926240553402</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3609,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
@@ -3640,7 +3649,7 @@
         <v>5055.6463923269803</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3669,7 +3678,7 @@
         <v>256.65462685736219</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3698,7 +3707,7 @@
         <v>21.970980528720091</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3725,7 +3734,7 @@
         <v>217.88072015961899</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3752,7 +3761,7 @@
         <v>23651.094357414571</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
@@ -3783,7 +3792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3812,7 +3821,7 @@
         <v>76.518056508623246</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3841,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3868,7 +3877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3895,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2" t="s">
@@ -3926,7 +3935,7 @@
         <v>13403.29488744485</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3955,7 +3964,7 @@
         <v>2051.8987971185711</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -3984,7 +3993,7 @@
         <v>894.26852323064577</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4013,7 +4022,7 @@
         <v>670.47741529346615</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4040,7 +4049,7 @@
         <v>69.992323717012312</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4069,7 +4078,7 @@
         <v>497.76753799776839</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4098,7 +4107,7 @@
         <v>109.3222562653724</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4127,7 +4136,7 @@
         <v>1220.918915716185</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4156,7 +4165,7 @@
         <v>8597.491978468106</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4185,7 +4194,7 @@
         <v>3853.8330792285951</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4214,7 +4223,7 @@
         <v>297.82901487541579</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4243,7 +4252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4272,7 +4281,7 @@
         <v>2297.5608562399052</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4301,7 +4310,7 @@
         <v>1310.6758990906501</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4330,7 +4339,7 @@
         <v>180.3281421367605</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4359,7 +4368,7 @@
         <v>37.372037338883899</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4388,7 +4397,7 @@
         <v>2197.768690212175</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4417,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4446,7 +4455,7 @@
         <v>312.70406489999237</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4475,7 +4484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4504,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4531,7 +4540,7 @@
         <v>9805.6320587312475</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4558,7 +4567,7 @@
         <v>40094.453078762817</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4585,7 +4594,7 @@
         <v>1939.157029876385</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -4612,7 +4621,7 @@
         <v>18281.610207512062</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4639,7 +4648,7 @@
         <v>14299.26338849785</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -4666,7 +4675,7 @@
         <v>17301.268441043911</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4695,7 +4704,7 @@
         <v>44449.491151360453</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -4722,7 +4731,7 @@
         <v>50542.22118209883</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4751,7 +4760,7 @@
         <v>13120.713589184999</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4778,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4805,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
@@ -4836,7 +4845,7 @@
         <v>108.32702368021729</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -4863,7 +4872,7 @@
         <v>246.08331151248029</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4890,7 +4899,7 @@
         <v>4938.8740901772526</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -4917,7 +4926,7 @@
         <v>614.6587414930209</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4944,7 +4953,7 @@
         <v>239.90906455272119</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -4971,7 +4980,7 @@
         <v>21.62830862846565</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4998,7 +5007,7 @@
         <v>105.239383486877</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -5025,7 +5034,7 @@
         <v>81.969710005592361</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -5052,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -5079,7 +5088,7 @@
         <v>5.4637311254154382</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -5106,7 +5115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5133,7 +5142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5162,7 +5171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5189,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5218,7 +5227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5245,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5272,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5299,7 +5308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5328,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5357,7 +5366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5386,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="1" t="s">
@@ -5417,7 +5426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2" t="s">
@@ -5448,7 +5457,7 @@
         <v>5047.2749343290261</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5475,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2" t="s">
@@ -5506,7 +5515,7 @@
         <v>2570.428917715521</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5535,7 +5544,7 @@
         <v>260.1732094158657</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -5562,7 +5571,7 @@
         <v>9893.4277908268996</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5589,7 +5598,7 @@
         <v>7340.245761190954</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -5618,7 +5627,7 @@
         <v>48343.181025040598</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2" t="s">
@@ -5649,7 +5658,7 @@
         <v>3039.3679876111569</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -5676,7 +5685,7 @@
         <v>9642.6799831479275</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -5703,7 +5712,7 @@
         <v>614.65359843593114</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -5732,7 +5741,7 @@
         <v>8665.8685083556247</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -5759,7 +5768,7 @@
         <v>107.2284965695295</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -5788,7 +5797,7 @@
         <v>12455.283861336849</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2" t="s">
@@ -5819,7 +5828,7 @@
         <v>6559.3803686860874</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -5846,7 +5855,7 @@
         <v>6290.8659550271468</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5873,7 +5882,7 @@
         <v>5910.5952484080899</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -5900,7 +5909,7 @@
         <v>4015.7947097559522</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5927,7 +5936,7 @@
         <v>1127.4379359350521</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -5954,7 +5963,7 @@
         <v>8700.5294822484502</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -5981,7 +5990,7 @@
         <v>3030.50310291194</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -6008,7 +6017,7 @@
         <v>5650.4271236598343</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -6035,7 +6044,7 @@
         <v>6418.7945683399457</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6062,7 +6071,7 @@
         <v>42645.631263254043</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -6091,7 +6100,7 @@
         <v>1461.6928387552571</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -6118,7 +6127,7 @@
         <v>1063.8706844738699</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -6145,7 +6154,7 @@
         <v>1181.6349326867751</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2" t="s">
@@ -6176,7 +6185,7 @@
         <v>45.172742483163432</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -6203,7 +6212,7 @@
         <v>47.941269140624911</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -6230,7 +6239,7 @@
         <v>28.898748130341641</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6257,7 +6266,7 @@
         <v>99.671791583933668</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6284,7 +6293,7 @@
         <v>10.296308766356089</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6311,7 +6320,7 @@
         <v>19.327712785136491</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6338,7 +6347,7 @@
         <v>53.454329439570273</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6367,7 +6376,7 @@
         <v>5.8767212313858366</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6394,7 +6403,7 @@
         <v>0.79381119257476329</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6421,7 +6430,7 @@
         <v>38.354780343140668</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6448,7 +6457,7 @@
         <v>43.594271398071577</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6475,7 +6484,7 @@
         <v>1.0171060223917621</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6504,7 +6513,7 @@
         <v>19.43030599946859</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6531,7 +6540,7 @@
         <v>32.762968188353632</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -6560,7 +6569,7 @@
         <v>34.163142175287078</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -6587,7 +6596,7 @@
         <v>26.115440666887132</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -6614,7 +6623,7 @@
         <v>7.3636648867077694</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -6641,7 +6650,7 @@
         <v>61.315217072728743</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -6668,7 +6677,7 @@
         <v>5.0045067815524389</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -6695,7 +6704,7 @@
         <v>10.677249379984341</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2" t="s">
@@ -6726,7 +6735,7 @@
         <v>82.701061044636049</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -6753,7 +6762,7 @@
         <v>2856.4540370088198</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -6780,7 +6789,7 @@
         <v>319.33123408778749</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -6807,7 +6816,7 @@
         <v>8949.5483838491873</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -6834,7 +6843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A205" s="2" t="s">
         <v>261</v>
       </c>
@@ -6869,7 +6878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -6896,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -6923,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -6950,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -6977,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -7004,7 +7013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -7031,7 +7040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -7058,7 +7067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -7087,7 +7096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -7114,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -7141,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -7168,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -7195,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -7222,7 +7231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -7249,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -7276,7 +7285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -7303,7 +7312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -7332,7 +7341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -7361,7 +7370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2" t="s">
@@ -7392,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -7419,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -7446,7 +7455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -7473,7 +7482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -7500,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -7527,7 +7536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -7554,7 +7563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -7581,7 +7590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -7608,7 +7617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -7635,7 +7644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -7662,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -7689,7 +7698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -7718,7 +7727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -7745,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -7772,7 +7781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -7799,7 +7808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -7826,7 +7835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -7853,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -7880,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -7907,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -7936,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -7963,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -7990,7 +7999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2" t="s">
@@ -8021,7 +8030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -8048,7 +8057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -8075,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8102,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8129,7 +8138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8156,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8183,7 +8192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8210,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8237,7 +8246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8264,7 +8273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -8291,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -8318,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -8347,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -8374,7 +8383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -8401,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -8430,7 +8439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -8459,7 +8468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -8488,7 +8497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -8517,7 +8526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -8546,7 +8555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -8575,7 +8584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2" t="s">
@@ -8606,7 +8615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -8633,7 +8642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -8660,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -8689,7 +8698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -8716,7 +8725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -8743,7 +8752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -8770,7 +8779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -8797,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -8824,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -8853,7 +8862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -8880,7 +8889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -8909,7 +8918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -8938,7 +8947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -8965,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -8992,7 +9001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -9019,7 +9028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -9046,7 +9055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -9073,7 +9082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -9100,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -9127,7 +9136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -9154,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -9183,7 +9192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2" t="s">
@@ -9214,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -9243,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -9272,7 +9281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -9299,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -9326,7 +9335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2" t="s">
@@ -9357,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -9386,7 +9395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -9415,7 +9424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -9442,7 +9451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -9469,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2" t="s">
@@ -9500,7 +9509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -9529,7 +9538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -9558,7 +9567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -9587,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -9614,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -9643,7 +9652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -9672,7 +9681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -9701,7 +9710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -9730,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -9759,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -9788,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -9817,7 +9826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -9846,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -9875,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -9904,7 +9913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -9933,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -9962,7 +9971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -9991,7 +10000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -10020,7 +10029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -10049,7 +10058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -10078,7 +10087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -10105,7 +10114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -10132,7 +10141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -10159,7 +10168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -10186,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -10213,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -10240,7 +10249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -10269,7 +10278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -10296,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -10325,7 +10334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -10352,7 +10361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -10379,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2" t="s">
@@ -10410,7 +10419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -10437,7 +10446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -10464,7 +10473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -10491,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -10518,7 +10527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -10545,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -10572,7 +10581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -10599,7 +10608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -10626,7 +10635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -10653,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -10680,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -10707,7 +10716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -10736,7 +10745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -10763,7 +10772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -10792,7 +10801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -10819,7 +10828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -10846,7 +10855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -10873,7 +10882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -10902,7 +10911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -10931,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -10960,7 +10969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="1" t="s">
@@ -10991,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2" t="s">
@@ -11022,7 +11031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -11049,7 +11058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2" t="s">
@@ -11080,7 +11089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -11109,7 +11118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -11136,7 +11145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -11163,7 +11172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -11192,7 +11201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2" t="s">
@@ -11223,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -11250,7 +11259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -11277,7 +11286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -11306,7 +11315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -11333,7 +11342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -11362,7 +11371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2" t="s">
@@ -11393,7 +11402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -11420,7 +11429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -11447,7 +11456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -11474,7 +11483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -11501,7 +11510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -11528,7 +11537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -11555,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -11582,7 +11591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -11609,7 +11618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -11636,7 +11645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -11665,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -11692,7 +11701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -11719,7 +11728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2" t="s">
@@ -11750,7 +11759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -11777,7 +11786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -11804,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -11831,7 +11840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -11858,7 +11867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -11885,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -11912,7 +11921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -11941,7 +11950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -11968,7 +11977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -11995,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -12022,7 +12031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -12049,7 +12058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -12078,7 +12087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -12105,7 +12114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -12134,7 +12143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -12161,7 +12170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -12188,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -12215,7 +12224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -12242,7 +12251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -12269,7 +12278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2" t="s">
@@ -12300,7 +12309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -12327,7 +12336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -12354,7 +12363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -12381,7 +12390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -12410,6 +12419,86 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A5:A204"/>
+    <mergeCell ref="D280:D288"/>
+    <mergeCell ref="C200:C204"/>
+    <mergeCell ref="D71:D76"/>
+    <mergeCell ref="D47:D58"/>
+    <mergeCell ref="D244:D246"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="C24:C46"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C90:C94"/>
+    <mergeCell ref="A205:A404"/>
+    <mergeCell ref="C5:C23"/>
+    <mergeCell ref="D13:D21"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="D377:D379"/>
+    <mergeCell ref="D332:D343"/>
+    <mergeCell ref="D354:D355"/>
+    <mergeCell ref="D271:D276"/>
+    <mergeCell ref="C95:C99"/>
+    <mergeCell ref="D180:D186"/>
+    <mergeCell ref="C167:C179"/>
+    <mergeCell ref="D327:D328"/>
+    <mergeCell ref="C268:C289"/>
+    <mergeCell ref="D303:D304"/>
+    <mergeCell ref="D177:D179"/>
+    <mergeCell ref="D161:D163"/>
+    <mergeCell ref="C224:C246"/>
+    <mergeCell ref="D129:D131"/>
+    <mergeCell ref="D277:D278"/>
+    <mergeCell ref="D194:D199"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C100:C131"/>
+    <mergeCell ref="C205:C223"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="C132:C152"/>
+    <mergeCell ref="D80:D88"/>
+    <mergeCell ref="D120:D126"/>
+    <mergeCell ref="D167:D176"/>
+    <mergeCell ref="C180:C199"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="C161:C166"/>
+    <mergeCell ref="D392:D393"/>
+    <mergeCell ref="D187:D191"/>
+    <mergeCell ref="D361:D363"/>
+    <mergeCell ref="B205:B404"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="D344:D345"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="C156:C160"/>
+    <mergeCell ref="D200:D204"/>
+    <mergeCell ref="D268:D270"/>
+    <mergeCell ref="D236:D243"/>
+    <mergeCell ref="B5:B204"/>
+    <mergeCell ref="C290:C294"/>
+    <mergeCell ref="C68:C89"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="C361:C366"/>
+    <mergeCell ref="D387:D391"/>
+    <mergeCell ref="D394:D399"/>
+    <mergeCell ref="D364:D365"/>
+    <mergeCell ref="C367:C379"/>
+    <mergeCell ref="D205:D212"/>
+    <mergeCell ref="C300:C331"/>
+    <mergeCell ref="D292:D294"/>
+    <mergeCell ref="C295:C299"/>
+    <mergeCell ref="D357:D359"/>
+    <mergeCell ref="D380:D386"/>
+    <mergeCell ref="D213:D221"/>
+    <mergeCell ref="D259:D261"/>
+    <mergeCell ref="C356:C360"/>
+    <mergeCell ref="C354:C355"/>
+    <mergeCell ref="C247:C267"/>
+    <mergeCell ref="D224:D235"/>
     <mergeCell ref="C400:C404"/>
     <mergeCell ref="D132:D143"/>
     <mergeCell ref="F2:H2"/>
@@ -12426,92 +12515,27 @@
     <mergeCell ref="D297:D299"/>
     <mergeCell ref="C332:C352"/>
     <mergeCell ref="D367:D376"/>
-    <mergeCell ref="D387:D391"/>
-    <mergeCell ref="D394:D399"/>
-    <mergeCell ref="D364:D365"/>
-    <mergeCell ref="C367:C379"/>
-    <mergeCell ref="D205:D212"/>
-    <mergeCell ref="C300:C331"/>
-    <mergeCell ref="D292:D294"/>
-    <mergeCell ref="C295:C299"/>
-    <mergeCell ref="D357:D359"/>
-    <mergeCell ref="D380:D386"/>
-    <mergeCell ref="D213:D221"/>
-    <mergeCell ref="D259:D261"/>
-    <mergeCell ref="C356:C360"/>
-    <mergeCell ref="C354:C355"/>
-    <mergeCell ref="C247:C267"/>
-    <mergeCell ref="D224:D235"/>
-    <mergeCell ref="D392:D393"/>
-    <mergeCell ref="D187:D191"/>
-    <mergeCell ref="D361:D363"/>
-    <mergeCell ref="B205:B404"/>
-    <mergeCell ref="D127:D128"/>
-    <mergeCell ref="D344:D345"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="D200:D204"/>
-    <mergeCell ref="D268:D270"/>
-    <mergeCell ref="D236:D243"/>
-    <mergeCell ref="B5:B204"/>
-    <mergeCell ref="C290:C294"/>
-    <mergeCell ref="C68:C89"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="C361:C366"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="C100:C131"/>
-    <mergeCell ref="C205:C223"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="C132:C152"/>
-    <mergeCell ref="D80:D88"/>
-    <mergeCell ref="D120:D126"/>
-    <mergeCell ref="D167:D176"/>
-    <mergeCell ref="C180:C199"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="C161:C166"/>
-    <mergeCell ref="D377:D379"/>
-    <mergeCell ref="D332:D343"/>
-    <mergeCell ref="D354:D355"/>
-    <mergeCell ref="D271:D276"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="D180:D186"/>
-    <mergeCell ref="C167:C179"/>
-    <mergeCell ref="D327:D328"/>
-    <mergeCell ref="C268:C289"/>
-    <mergeCell ref="D303:D304"/>
-    <mergeCell ref="D177:D179"/>
-    <mergeCell ref="D161:D163"/>
-    <mergeCell ref="C224:C246"/>
-    <mergeCell ref="D129:D131"/>
-    <mergeCell ref="D277:D278"/>
-    <mergeCell ref="D194:D199"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A5:A204"/>
-    <mergeCell ref="D280:D288"/>
-    <mergeCell ref="C200:C204"/>
-    <mergeCell ref="D71:D76"/>
-    <mergeCell ref="D47:D58"/>
-    <mergeCell ref="D244:D246"/>
-    <mergeCell ref="D24:D35"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="C24:C46"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C90:C94"/>
-    <mergeCell ref="A205:A404"/>
-    <mergeCell ref="C5:C23"/>
-    <mergeCell ref="D13:D21"/>
-    <mergeCell ref="D59:D61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDDBE4AC5AD34144A319C175B124CDA5" ma:contentTypeVersion="7" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fc6499810b9fd453994c0b215026778e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2a1cb09faa248fb1b7a5ebc9a370fc2" ns2:_="">
     <xsd:import namespace="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
@@ -12673,31 +12697,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3C4A7E-F953-428F-959B-BCAE46876222}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACCF20D5-FDC5-4A86-B645-F4CE7E7068A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACCF20D5-FDC5-4A86-B645-F4CE7E7068A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3C4A7E-F953-428F-959B-BCAE46876222}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/3.8.2/0. base-year_2015/system/Y.xlsx
+++ b/data/3.8.2/0. base-year_2015/system/Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\3.8.2\0. base-year_2015\system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A81834-2663-42E9-94B6-A98E4296AC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204E9536-23EA-48FE-A56D-983CCD71A14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12419,6 +12419,86 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="C400:C404"/>
+    <mergeCell ref="D132:D143"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="D247:D258"/>
+    <mergeCell ref="D92:D94"/>
+    <mergeCell ref="C380:C399"/>
+    <mergeCell ref="D346:D349"/>
+    <mergeCell ref="D36:D43"/>
+    <mergeCell ref="D329:D331"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="C47:C67"/>
+    <mergeCell ref="D320:D326"/>
+    <mergeCell ref="D192:D193"/>
+    <mergeCell ref="D297:D299"/>
+    <mergeCell ref="C332:C352"/>
+    <mergeCell ref="D367:D376"/>
+    <mergeCell ref="D387:D391"/>
+    <mergeCell ref="D394:D399"/>
+    <mergeCell ref="D364:D365"/>
+    <mergeCell ref="C367:C379"/>
+    <mergeCell ref="D205:D212"/>
+    <mergeCell ref="C300:C331"/>
+    <mergeCell ref="D292:D294"/>
+    <mergeCell ref="C295:C299"/>
+    <mergeCell ref="D357:D359"/>
+    <mergeCell ref="D380:D386"/>
+    <mergeCell ref="D213:D221"/>
+    <mergeCell ref="D259:D261"/>
+    <mergeCell ref="C356:C360"/>
+    <mergeCell ref="C354:C355"/>
+    <mergeCell ref="C247:C267"/>
+    <mergeCell ref="D224:D235"/>
+    <mergeCell ref="D392:D393"/>
+    <mergeCell ref="D187:D191"/>
+    <mergeCell ref="D361:D363"/>
+    <mergeCell ref="B205:B404"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="D344:D345"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="C156:C160"/>
+    <mergeCell ref="D200:D204"/>
+    <mergeCell ref="D268:D270"/>
+    <mergeCell ref="D236:D243"/>
+    <mergeCell ref="B5:B204"/>
+    <mergeCell ref="C290:C294"/>
+    <mergeCell ref="C68:C89"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="C361:C366"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C100:C131"/>
+    <mergeCell ref="C205:C223"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="C132:C152"/>
+    <mergeCell ref="D80:D88"/>
+    <mergeCell ref="D120:D126"/>
+    <mergeCell ref="D167:D176"/>
+    <mergeCell ref="C180:C199"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="C161:C166"/>
+    <mergeCell ref="D377:D379"/>
+    <mergeCell ref="D332:D343"/>
+    <mergeCell ref="D354:D355"/>
+    <mergeCell ref="D271:D276"/>
+    <mergeCell ref="C95:C99"/>
+    <mergeCell ref="D180:D186"/>
+    <mergeCell ref="C167:C179"/>
+    <mergeCell ref="D327:D328"/>
+    <mergeCell ref="C268:C289"/>
+    <mergeCell ref="D303:D304"/>
+    <mergeCell ref="D177:D179"/>
+    <mergeCell ref="D161:D163"/>
+    <mergeCell ref="C224:C246"/>
+    <mergeCell ref="D129:D131"/>
+    <mergeCell ref="D277:D278"/>
+    <mergeCell ref="D194:D199"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="A5:A204"/>
     <mergeCell ref="D280:D288"/>
@@ -12435,86 +12515,6 @@
     <mergeCell ref="C5:C23"/>
     <mergeCell ref="D13:D21"/>
     <mergeCell ref="D59:D61"/>
-    <mergeCell ref="D377:D379"/>
-    <mergeCell ref="D332:D343"/>
-    <mergeCell ref="D354:D355"/>
-    <mergeCell ref="D271:D276"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="D180:D186"/>
-    <mergeCell ref="C167:C179"/>
-    <mergeCell ref="D327:D328"/>
-    <mergeCell ref="C268:C289"/>
-    <mergeCell ref="D303:D304"/>
-    <mergeCell ref="D177:D179"/>
-    <mergeCell ref="D161:D163"/>
-    <mergeCell ref="C224:C246"/>
-    <mergeCell ref="D129:D131"/>
-    <mergeCell ref="D277:D278"/>
-    <mergeCell ref="D194:D199"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="C100:C131"/>
-    <mergeCell ref="C205:C223"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="C132:C152"/>
-    <mergeCell ref="D80:D88"/>
-    <mergeCell ref="D120:D126"/>
-    <mergeCell ref="D167:D176"/>
-    <mergeCell ref="C180:C199"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="C161:C166"/>
-    <mergeCell ref="D392:D393"/>
-    <mergeCell ref="D187:D191"/>
-    <mergeCell ref="D361:D363"/>
-    <mergeCell ref="B205:B404"/>
-    <mergeCell ref="D127:D128"/>
-    <mergeCell ref="D344:D345"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="D200:D204"/>
-    <mergeCell ref="D268:D270"/>
-    <mergeCell ref="D236:D243"/>
-    <mergeCell ref="B5:B204"/>
-    <mergeCell ref="C290:C294"/>
-    <mergeCell ref="C68:C89"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="C361:C366"/>
-    <mergeCell ref="D387:D391"/>
-    <mergeCell ref="D394:D399"/>
-    <mergeCell ref="D364:D365"/>
-    <mergeCell ref="C367:C379"/>
-    <mergeCell ref="D205:D212"/>
-    <mergeCell ref="C300:C331"/>
-    <mergeCell ref="D292:D294"/>
-    <mergeCell ref="C295:C299"/>
-    <mergeCell ref="D357:D359"/>
-    <mergeCell ref="D380:D386"/>
-    <mergeCell ref="D213:D221"/>
-    <mergeCell ref="D259:D261"/>
-    <mergeCell ref="C356:C360"/>
-    <mergeCell ref="C354:C355"/>
-    <mergeCell ref="C247:C267"/>
-    <mergeCell ref="D224:D235"/>
-    <mergeCell ref="C400:C404"/>
-    <mergeCell ref="D132:D143"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="D247:D258"/>
-    <mergeCell ref="D92:D94"/>
-    <mergeCell ref="C380:C399"/>
-    <mergeCell ref="D346:D349"/>
-    <mergeCell ref="D36:D43"/>
-    <mergeCell ref="D329:D331"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="C47:C67"/>
-    <mergeCell ref="D320:D326"/>
-    <mergeCell ref="D192:D193"/>
-    <mergeCell ref="D297:D299"/>
-    <mergeCell ref="C332:C352"/>
-    <mergeCell ref="D367:D376"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12527,15 +12527,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDDBE4AC5AD34144A319C175B124CDA5" ma:contentTypeVersion="7" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fc6499810b9fd453994c0b215026778e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2a1cb09faa248fb1b7a5ebc9a370fc2" ns2:_="">
     <xsd:import namespace="df3242dc-6eaf-41b4-ba9f-f9ed2a2fc658"/>
@@ -12697,6 +12688,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACCF20D5-FDC5-4A86-B645-F4CE7E7068A4}">
   <ds:schemaRefs>
@@ -12707,14 +12707,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE3C4A7E-F953-428F-959B-BCAE46876222}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12732,6 +12724,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{98ce3bfb-fff1-481a-835b-0a342757958d}" enabled="1" method="Standard" siteId="{cb6c2492-4a85-4b15-85a1-ed94d47e5849}" removed="0"/>

--- a/data/3.8.2/0. base-year_2015/system/Y.xlsx
+++ b/data/3.8.2/0. base-year_2015/system/Y.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\3.8.2\0. base-year_2015\system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204E9536-23EA-48FE-A56D-983CCD71A14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FFF70B-BEDB-4CB5-A58C-800542E79F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12419,6 +12419,86 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="A5:A204"/>
+    <mergeCell ref="D280:D288"/>
+    <mergeCell ref="C200:C204"/>
+    <mergeCell ref="D71:D76"/>
+    <mergeCell ref="D47:D58"/>
+    <mergeCell ref="D244:D246"/>
+    <mergeCell ref="D24:D35"/>
+    <mergeCell ref="C154:C155"/>
+    <mergeCell ref="C24:C46"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="C90:C94"/>
+    <mergeCell ref="A205:A404"/>
+    <mergeCell ref="C5:C23"/>
+    <mergeCell ref="D13:D21"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="D377:D379"/>
+    <mergeCell ref="D332:D343"/>
+    <mergeCell ref="D354:D355"/>
+    <mergeCell ref="D271:D276"/>
+    <mergeCell ref="C95:C99"/>
+    <mergeCell ref="D180:D186"/>
+    <mergeCell ref="C167:C179"/>
+    <mergeCell ref="D327:D328"/>
+    <mergeCell ref="C268:C289"/>
+    <mergeCell ref="D303:D304"/>
+    <mergeCell ref="D177:D179"/>
+    <mergeCell ref="D161:D163"/>
+    <mergeCell ref="C224:C246"/>
+    <mergeCell ref="D129:D131"/>
+    <mergeCell ref="D277:D278"/>
+    <mergeCell ref="D194:D199"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="C100:C131"/>
+    <mergeCell ref="C205:C223"/>
+    <mergeCell ref="D164:D165"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="C132:C152"/>
+    <mergeCell ref="D80:D88"/>
+    <mergeCell ref="D120:D126"/>
+    <mergeCell ref="D167:D176"/>
+    <mergeCell ref="C180:C199"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="D154:D155"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="C161:C166"/>
+    <mergeCell ref="D392:D393"/>
+    <mergeCell ref="D187:D191"/>
+    <mergeCell ref="D361:D363"/>
+    <mergeCell ref="B205:B404"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="D344:D345"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="C156:C160"/>
+    <mergeCell ref="D200:D204"/>
+    <mergeCell ref="D268:D270"/>
+    <mergeCell ref="D236:D243"/>
+    <mergeCell ref="B5:B204"/>
+    <mergeCell ref="C290:C294"/>
+    <mergeCell ref="C68:C89"/>
+    <mergeCell ref="D400:D404"/>
+    <mergeCell ref="C361:C366"/>
+    <mergeCell ref="D387:D391"/>
+    <mergeCell ref="D394:D399"/>
+    <mergeCell ref="D364:D365"/>
+    <mergeCell ref="C367:C379"/>
+    <mergeCell ref="D205:D212"/>
+    <mergeCell ref="C300:C331"/>
+    <mergeCell ref="D292:D294"/>
+    <mergeCell ref="C295:C299"/>
+    <mergeCell ref="D357:D359"/>
+    <mergeCell ref="D380:D386"/>
+    <mergeCell ref="D213:D221"/>
+    <mergeCell ref="D259:D261"/>
+    <mergeCell ref="C356:C360"/>
+    <mergeCell ref="C354:C355"/>
+    <mergeCell ref="C247:C267"/>
+    <mergeCell ref="D224:D235"/>
     <mergeCell ref="C400:C404"/>
     <mergeCell ref="D132:D143"/>
     <mergeCell ref="F2:H2"/>
@@ -12435,95 +12515,18 @@
     <mergeCell ref="D297:D299"/>
     <mergeCell ref="C332:C352"/>
     <mergeCell ref="D367:D376"/>
-    <mergeCell ref="D387:D391"/>
-    <mergeCell ref="D394:D399"/>
-    <mergeCell ref="D364:D365"/>
-    <mergeCell ref="C367:C379"/>
-    <mergeCell ref="D205:D212"/>
-    <mergeCell ref="C300:C331"/>
-    <mergeCell ref="D292:D294"/>
-    <mergeCell ref="C295:C299"/>
-    <mergeCell ref="D357:D359"/>
-    <mergeCell ref="D380:D386"/>
-    <mergeCell ref="D213:D221"/>
-    <mergeCell ref="D259:D261"/>
-    <mergeCell ref="C356:C360"/>
-    <mergeCell ref="C354:C355"/>
-    <mergeCell ref="C247:C267"/>
-    <mergeCell ref="D224:D235"/>
-    <mergeCell ref="D392:D393"/>
-    <mergeCell ref="D187:D191"/>
-    <mergeCell ref="D361:D363"/>
-    <mergeCell ref="B205:B404"/>
-    <mergeCell ref="D127:D128"/>
-    <mergeCell ref="D344:D345"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="D200:D204"/>
-    <mergeCell ref="D268:D270"/>
-    <mergeCell ref="D236:D243"/>
-    <mergeCell ref="B5:B204"/>
-    <mergeCell ref="C290:C294"/>
-    <mergeCell ref="C68:C89"/>
-    <mergeCell ref="D400:D404"/>
-    <mergeCell ref="C361:C366"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="C100:C131"/>
-    <mergeCell ref="C205:C223"/>
-    <mergeCell ref="D164:D165"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="C132:C152"/>
-    <mergeCell ref="D80:D88"/>
-    <mergeCell ref="D120:D126"/>
-    <mergeCell ref="D167:D176"/>
-    <mergeCell ref="C180:C199"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="D154:D155"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="C161:C166"/>
-    <mergeCell ref="D377:D379"/>
-    <mergeCell ref="D332:D343"/>
-    <mergeCell ref="D354:D355"/>
-    <mergeCell ref="D271:D276"/>
-    <mergeCell ref="C95:C99"/>
-    <mergeCell ref="D180:D186"/>
-    <mergeCell ref="C167:C179"/>
-    <mergeCell ref="D327:D328"/>
-    <mergeCell ref="C268:C289"/>
-    <mergeCell ref="D303:D304"/>
-    <mergeCell ref="D177:D179"/>
-    <mergeCell ref="D161:D163"/>
-    <mergeCell ref="C224:C246"/>
-    <mergeCell ref="D129:D131"/>
-    <mergeCell ref="D277:D278"/>
-    <mergeCell ref="D194:D199"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="A5:A204"/>
-    <mergeCell ref="D280:D288"/>
-    <mergeCell ref="C200:C204"/>
-    <mergeCell ref="D71:D76"/>
-    <mergeCell ref="D47:D58"/>
-    <mergeCell ref="D244:D246"/>
-    <mergeCell ref="D24:D35"/>
-    <mergeCell ref="C154:C155"/>
-    <mergeCell ref="C24:C46"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="C90:C94"/>
-    <mergeCell ref="A205:A404"/>
-    <mergeCell ref="C5:C23"/>
-    <mergeCell ref="D13:D21"/>
-    <mergeCell ref="D59:D61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12689,19 +12692,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACCF20D5-FDC5-4A86-B645-F4CE7E7068A4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12725,9 +12724,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7A28FB-A954-44EA-94B5-D2337D683276}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACCF20D5-FDC5-4A86-B645-F4CE7E7068A4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
